--- a/audit_report_ALL_TEAM_19_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -851,10 +851,8 @@
           <t>Poonam Thapa</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9848029115</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9848029115</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -889,10 +887,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>27.74773</t>
-        </is>
+      <c r="Y2" s="3" t="n">
+        <v>27.74773</v>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
@@ -944,25 +940,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>L7-8</t>
         </is>
       </c>
-      <c r="AP2" s="3" t="inlineStr">
-        <is>
-          <t>85.32958</t>
-        </is>
+      <c r="AP2" s="3" t="n">
+        <v>85.32958000000001</v>
       </c>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr">
@@ -1048,20 +1040,14 @@
           <t>On Hold</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr">
         <is>
           <t>Prabin Mainali</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9851330557</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9851330557</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1143,10 +1129,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
@@ -1157,7 +1141,7 @@
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr">
@@ -1243,20 +1227,14 @@
           <t>On Hold</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M4" s="3" t="inlineStr"/>
       <c r="N4" s="3" t="inlineStr">
         <is>
           <t>Shyam sapkota</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9851206430</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9851206430</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1291,10 +1269,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
@@ -1346,25 +1322,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>CDB472</t>
         </is>
       </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>Case : Extender installation  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_19_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW4"/>
+  <dimension ref="A1:AW7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -496,10 +496,10 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="25" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -512,7 +512,7 @@
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="11" customWidth="1" min="25" max="25"/>
     <col width="25" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
@@ -529,10 +529,10 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="32" customWidth="1" min="47" max="47"/>
+    <col width="36" customWidth="1" min="47" max="47"/>
     <col width="40" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
   </cols>
@@ -1362,6 +1362,631 @@
       <c r="AW4" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 9:39 AM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>TKT1374245</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Sanam Dura</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Sanam Dura</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>9845791679</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 09:39:53 AM</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>9845791679</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:34:49 PM</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 09:47:15 AM</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>27.76114</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>Budhanilkantha near Hello Kids Academy Montessori School, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>sanamdura18@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr"/>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>Binod Dhami</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>L16-4</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr">
+        <is>
+          <t>85.35745</t>
+        </is>
+      </c>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>7m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>21h 12m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 9:37 AM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>TKT1374011</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Sirjana kumari chand</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Sirjana kumari chand</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>9841124691</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 09:37:25 AM</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>9841124691</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 06:29:26 AM</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 09:37:25 AM</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>27.7499</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>Balkhu Dhapasi height , danphe basti, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>sirjana1chand@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr"/>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>1,13</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr">
+        <is>
+          <t>85.33821</t>
+        </is>
+      </c>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 7m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 9:34 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TKT1374291</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Sarad Tamang</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Sarad Tamang</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>9851085081</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 09:42:30 AM</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>CHB9851085081</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 01:47:48 PM</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 09:42:30 AM</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>Jeevan Tara Academy - Higher secondary school Kathmandu 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>9851085081@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI7" s="3" t="inlineStr"/>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Binod Dhami</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>L37-6</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>19h 54m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -1413,7 +2038,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -1499,7 +2124,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>0</v>
@@ -1575,7 +2200,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D15" s="5" t="n">
         <v>0</v>

--- a/audit_report_ALL_TEAM_19_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -1432,10 +1432,8 @@
           <t>Sanam Dura</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>9845791679</t>
-        </is>
+      <c r="O5" s="3" t="n">
+        <v>9845791679</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -1470,10 +1468,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>27.76114</t>
-        </is>
+      <c r="Y5" s="3" t="n">
+        <v>27.76114</v>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
@@ -1525,25 +1521,21 @@
           <t>Binod Dhami</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN5" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>L16-4</t>
         </is>
       </c>
-      <c r="AP5" s="3" t="inlineStr">
-        <is>
-          <t>85.35745</t>
-        </is>
+      <c r="AP5" s="3" t="n">
+        <v>85.35745</v>
       </c>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr">
@@ -1639,10 +1631,8 @@
           <t>Sirjana kumari chand</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>9841124691</t>
-        </is>
+      <c r="O6" s="3" t="n">
+        <v>9841124691</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -1677,10 +1667,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>27.7499</t>
-        </is>
+      <c r="Y6" s="3" t="n">
+        <v>27.7499</v>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
@@ -1732,25 +1720,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN6" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
           <t>1,13</t>
         </is>
       </c>
-      <c r="AP6" s="3" t="inlineStr">
-        <is>
-          <t>85.33821</t>
-        </is>
+      <c r="AP6" s="3" t="n">
+        <v>85.33821</v>
       </c>
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr">
@@ -1846,10 +1830,8 @@
           <t>Sarad Tamang</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9851085081</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9851085081</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -1884,10 +1866,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
@@ -1925,10 +1905,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH7" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH7" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI7" s="3" t="inlineStr"/>
       <c r="AJ7" s="3" t="inlineStr"/>
@@ -1943,25 +1921,21 @@
           <t>Binod Dhami</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
           <t>L37-6</t>
         </is>
       </c>
-      <c r="AP7" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_19_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Oct_2026.xlsx
@@ -483,11 +483,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW7"/>
+  <dimension ref="A1:AW8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -510,7 +510,7 @@
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
-    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
     <col width="25" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
@@ -520,7 +520,7 @@
     <col width="28" customWidth="1" min="32" max="32"/>
     <col width="32" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
-    <col width="10" customWidth="1" min="35" max="35"/>
+    <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
     <col width="18" customWidth="1" min="38" max="38"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -1959,6 +1959,213 @@
         </is>
       </c>
       <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 10:50 AM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1374083</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Sitaram Karki</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Sitaram Karki</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9860144229</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 10:50:02 AM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>9860144229</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 09:10:27 AM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 10:50:02 AM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>27.706164</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>Manohara 8, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr"/>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>00:50 hour</t>
+        </is>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>L24-7</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr">
+        <is>
+          <t>85.382631</t>
+        </is>
+      </c>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 39m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -1975,7 +2182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1983,12 +2190,12 @@
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="27" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="11" max="11"/>
     <col width="35" customWidth="1" min="12" max="12"/>
     <col width="34" customWidth="1" min="13" max="13"/>
   </cols>
@@ -2012,7 +2219,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -2022,7 +2229,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -2033,7 +2240,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
@@ -2045,7 +2252,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0m</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2264,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1d 1h 39m</t>
         </is>
       </c>
     </row>
@@ -2098,14 +2305,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -2174,14 +2381,14 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -2280,6 +2487,73 @@
       <c r="M19" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>TKT1374083</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Sitaram Karki</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 10:50:02 AM</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 09:10:27 AM</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 10:50:02 AM</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 39m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_19_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -2031,10 +2031,8 @@
           <t>Sitaram Karki</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9860144229</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9860144229</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -2069,10 +2067,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>27.706164</t>
-        </is>
+      <c r="Y8" s="3" t="n">
+        <v>27.706164</v>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
@@ -2124,25 +2120,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>L24-7</t>
         </is>
       </c>
-      <c r="AP8" s="3" t="inlineStr">
-        <is>
-          <t>85.382631</t>
-        </is>
+      <c r="AP8" s="3" t="n">
+        <v>85.382631</v>
       </c>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
@@ -2191,7 +2183,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2523,7 +2515,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_19_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW8"/>
+  <dimension ref="A1:AW9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2163,6 +2163,109 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 11:20 AM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : Extender installation  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="inlineStr"/>
+      <c r="N9" s="3" t="inlineStr"/>
+      <c r="O9" s="3" t="inlineStr"/>
+      <c r="P9" s="3" t="inlineStr"/>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr"/>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr"/>
+      <c r="V9" s="3" t="inlineStr"/>
+      <c r="W9" s="3" t="inlineStr"/>
+      <c r="X9" s="3" t="inlineStr"/>
+      <c r="Y9" s="3" t="inlineStr"/>
+      <c r="Z9" s="3" t="inlineStr"/>
+      <c r="AA9" s="3" t="inlineStr"/>
+      <c r="AB9" s="3" t="inlineStr"/>
+      <c r="AC9" s="3" t="inlineStr"/>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr"/>
+      <c r="AF9" s="3" t="inlineStr"/>
+      <c r="AG9" s="3" t="inlineStr"/>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr"/>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr"/>
+      <c r="AM9" s="3" t="inlineStr"/>
+      <c r="AN9" s="3" t="inlineStr"/>
+      <c r="AO9" s="3" t="inlineStr"/>
+      <c r="AP9" s="3" t="inlineStr"/>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : Extender installation  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2174,7 +2277,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2211,7 +2314,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -2232,7 +2335,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -2326,224 +2429,253 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr"/>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
           <t>Mesh Connectivity</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Extender Installation Request</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="C17" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D17" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr"/>
+      <c r="B18" s="3" t="inlineStr"/>
+      <c r="C18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="K21" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="M21" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>TKT1374083</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Sitaram Karki</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>19 Oct 2026 10:50:02 AM</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>18 Oct 2026 09:10:27 AM</t>
         </is>
       </c>
-      <c r="K20" s="3" t="inlineStr">
+      <c r="K22" s="3" t="inlineStr">
         <is>
           <t>19 Oct 2026 10:50:02 AM</t>
         </is>
       </c>
-      <c r="L20" s="3" t="inlineStr">
+      <c r="L22" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M20" s="3" t="inlineStr">
+      <c r="M22" s="3" t="inlineStr">
         <is>
           <t>1d 1h 39m</t>
         </is>

--- a/audit_report_ALL_TEAM_19_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW9"/>
+  <dimension ref="A1:AW12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -515,9 +515,9 @@
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
-    <col width="10" customWidth="1" min="30" max="30"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="28" customWidth="1" min="32" max="32"/>
+    <col width="29" customWidth="1" min="32" max="32"/>
     <col width="32" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -2266,6 +2266,519 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 11:52 AM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : for wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>for wifi 6</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1374481</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Bidhya Syantang</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Bidhya Syantang</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9866371612</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 11:52:09 AM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>9851321498</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 06:34:55 PM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 11:52:09 AM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr"/>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>Somtirtha Gita Mandir gate - Hindu temple P93Q+7G9 Gita Mandir Rd Kageshwori Manohara 44600, Bagmati</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr"/>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr">
+        <is>
+          <t>01:52 hour</t>
+        </is>
+      </c>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Pradeep Yadav</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>L21-5</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr"/>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : for wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>17h 17m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : for wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 11:55 AM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case :  wifi 6 router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="3" t="inlineStr"/>
+      <c r="L11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr"/>
+      <c r="N11" s="3" t="inlineStr"/>
+      <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr"/>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr"/>
+      <c r="V11" s="3" t="inlineStr"/>
+      <c r="W11" s="3" t="inlineStr"/>
+      <c r="X11" s="3" t="inlineStr"/>
+      <c r="Y11" s="3" t="inlineStr"/>
+      <c r="Z11" s="3" t="inlineStr"/>
+      <c r="AA11" s="3" t="inlineStr"/>
+      <c r="AB11" s="3" t="inlineStr"/>
+      <c r="AC11" s="3" t="inlineStr"/>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr"/>
+      <c r="AF11" s="3" t="inlineStr"/>
+      <c r="AG11" s="3" t="inlineStr"/>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr"/>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr"/>
+      <c r="AM11" s="3" t="inlineStr"/>
+      <c r="AN11" s="3" t="inlineStr"/>
+      <c r="AO11" s="3" t="inlineStr"/>
+      <c r="AP11" s="3" t="inlineStr"/>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case :  wifi 6 router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 11:54 AM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : payment   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>payment</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1368992</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Nabina Shrestha</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Nabina Shrestha</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9841757149</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:37:29 PM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>9841757149</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 12:35:14 PM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 11:54:21 AM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>27.68717</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-CG Group</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>Opposite to SunShine High School, Satungal, kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr">
+        <is>
+          <t>nalinshrestha234@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr">
+        <is>
+          <t>01:19 hour</t>
+        </is>
+      </c>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr"/>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>CDB456</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>85.2412</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : payment   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>23h 16m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>5d 23h 19m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : payment   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2277,7 +2790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2286,7 +2799,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2314,7 +2827,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -2324,7 +2837,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -2335,7 +2848,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>27.3%</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2860,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>7h 45m</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2872,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 1h 39m</t>
+          <t>2d 14h 5m</t>
         </is>
       </c>
     </row>
@@ -2400,14 +2913,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>37.5%</t>
         </is>
       </c>
     </row>
@@ -2490,14 +3003,14 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>37.5%</t>
         </is>
       </c>
     </row>
@@ -2681,6 +3194,140 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>TKT1374481</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Bidhya Syantang</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Case : for wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Case : for wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 11:52:09 AM</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 06:34:55 PM</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 11:52:09 AM</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>17h 17m</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1368992</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Nabina Shrestha</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Case : payment   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : payment   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:37:29 PM</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 12:35:14 PM</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 11:54:21 AM</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>23h 16m</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>5d 23h 19m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_19_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -2333,10 +2333,8 @@
           <t>Bidhya Syantang</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9866371612</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9866371612</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -2422,10 +2420,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
@@ -2436,7 +2432,7 @@
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>Case : for wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
@@ -2635,10 +2631,8 @@
           <t>Nabina Shrestha</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9841757149</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9841757149</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -2673,10 +2667,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>27.68717</t>
-        </is>
+      <c r="Y12" s="3" t="n">
+        <v>27.68717</v>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
@@ -2732,25 +2724,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
           <t>CDB456</t>
         </is>
       </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>85.2412</t>
-        </is>
+      <c r="AP12" s="3" t="n">
+        <v>85.24120000000001</v>
       </c>
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>Case : payment   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
@@ -2799,7 +2787,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -3227,7 +3215,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Case : for wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
@@ -3294,7 +3282,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Case : payment   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_19_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW12"/>
+  <dimension ref="A1:AW13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -2767,6 +2767,209 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 12:53 PM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>TKT1374525</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>MD Sakib</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>MD Sakib</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>9803054740</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 12:53:24 PM</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>BKT9803054740</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 07:43:37 PM</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 01:03:07 PM</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr"/>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr">
+        <is>
+          <t>Koteshwor Mahadevasthan. Details from Google Maps Mahadevsthan Marg, Kathmandu 44600, Kathmandu, Nep</t>
+        </is>
+      </c>
+      <c r="AF13" s="3" t="inlineStr">
+        <is>
+          <t>sakibrain260@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG13" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr">
+        <is>
+          <t>02:53 hour</t>
+        </is>
+      </c>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>Rahul Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>3,4</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr"/>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>9m</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>17h 19m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2778,7 +2981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2787,7 +2990,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2815,7 +3018,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -2825,7 +3028,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -2836,7 +3039,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -2848,7 +3051,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>7h 45m</t>
+          <t>5h 51m</t>
         </is>
       </c>
     </row>
@@ -2860,7 +3063,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 14h 5m</t>
+          <t>2d 2h 53m</t>
         </is>
       </c>
     </row>
@@ -2901,14 +3104,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>44.4%</t>
         </is>
       </c>
     </row>
@@ -2991,14 +3194,14 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>44.4%</t>
         </is>
       </c>
     </row>
@@ -3316,6 +3519,73 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>TKT1374525</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>MD Sakib</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 12:53:24 PM</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 07:43:37 PM</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 01:03:07 PM</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>9m</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>17h 19m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_19_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -2834,10 +2834,8 @@
           <t>MD Sakib</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>9803054740</t>
-        </is>
+      <c r="O13" s="3" t="n">
+        <v>9803054740</v>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
@@ -2927,10 +2925,8 @@
           <t>Rahul Chaudhary</t>
         </is>
       </c>
-      <c r="AN13" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN13" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
@@ -2941,7 +2937,7 @@
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
@@ -2990,7 +2986,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -3552,7 +3548,7 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_19_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW13"/>
+  <dimension ref="A1:AW14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -501,7 +501,7 @@
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="23" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
@@ -511,7 +511,7 @@
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="25" customWidth="1" min="26" max="26"/>
+    <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
@@ -523,13 +523,13 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="18" customWidth="1" min="38" max="38"/>
+    <col width="28" customWidth="1" min="38" max="38"/>
     <col width="20" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -2966,6 +2966,209 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 1:43 PM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light in router  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>no light in router</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>TKT1374642</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Shashi kumar thakur</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Shashi kumar thakur</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>9818217448</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 08:22:33 AM</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>KLK9818217448</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 08:08:43 AM</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 01:43:44 PM</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr"/>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr">
+        <is>
+          <t>Goldhunga Orchid Academy Goldhunga Orchid Academy - School P7WW+JJ5 Kathmandu 44600, Kathmandu, Nepa</t>
+        </is>
+      </c>
+      <c r="AF14" s="3" t="inlineStr">
+        <is>
+          <t>9818217448@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG14" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr">
+        <is>
+          <t>03:43 hour</t>
+        </is>
+      </c>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr">
+        <is>
+          <t>Roshan Yadav (L1 Support)</t>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>L58-2</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr"/>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light in router  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>5h 21m</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>5h 35m</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light in router  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2977,16 +3180,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -3014,7 +3217,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -3024,7 +3227,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -3035,7 +3238,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>38.5%</t>
         </is>
       </c>
     </row>
@@ -3047,7 +3250,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>5h 51m</t>
+          <t>5h 45m</t>
         </is>
       </c>
     </row>
@@ -3059,7 +3262,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 2h 53m</t>
+          <t>1d 17h 50m</t>
         </is>
       </c>
     </row>
@@ -3114,349 +3317,256 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Mesh Connectivity</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr"/>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Mesh Connectivity</t>
+        </is>
+      </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr"/>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Total Scraped Tickets</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Solved / Handled Count</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>44.4%</t>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Total Scraped Tickets</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Solved / Handled Count</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Mesh Connectivity</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Extender Installation Request</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr"/>
-      <c r="B18" s="3" t="inlineStr"/>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
       <c r="C18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Mesh Connectivity</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Extender Installation Request</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr"/>
+      <c r="B20" s="3" t="inlineStr"/>
+      <c r="C20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="D20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M21" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>TKT1374083</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Sitaram Karki</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>19 Oct 2026 10:50:02 AM</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>18 Oct 2026 09:10:27 AM</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>19 Oct 2026 10:50:02 AM</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t>1d 1h 39m</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>TKT1374481</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Bidhya Syantang</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>Case : for wifi 6  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>19 Oct 2026 11:52:09 AM</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>18 Oct 2026 06:34:55 PM</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>19 Oct 2026 11:52:09 AM</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>17h 17m</t>
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>TKT1368992</t>
+          <t>TKT1374083</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Nabina Shrestha</t>
+          <t>Sitaram Karki</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -3471,12 +3581,12 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -3486,99 +3596,300 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Case : payment   has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>18 Oct 2026 12:37:29 PM</t>
+          <t>19 Oct 2026 10:50:02 AM</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>13 Oct 2026 12:35:14 PM</t>
+          <t>18 Oct 2026 09:10:27 AM</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>19 Oct 2026 11:54:21 AM</t>
+          <t>19 Oct 2026 10:50:02 AM</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>23h 16m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>5d 23h 19m</t>
+          <t>1d 1h 39m</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
+          <t>TKT1374481</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Bidhya Syantang</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>Case : for wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 11:52:09 AM</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 06:34:55 PM</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 11:52:09 AM</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>17h 17m</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1368992</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Nabina Shrestha</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : payment   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:37:29 PM</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 12:35:14 PM</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 11:54:21 AM</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>23h 16m</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>5d 23h 19m</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
           <t>TKT1374525</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>MD Sakib</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>Case : wifi 6   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>19 Oct 2026 12:53:24 PM</t>
         </is>
       </c>
-      <c r="J25" s="5" t="inlineStr">
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>18 Oct 2026 07:43:37 PM</t>
         </is>
       </c>
-      <c r="K25" s="5" t="inlineStr">
+      <c r="K27" s="5" t="inlineStr">
         <is>
           <t>19 Oct 2026 01:03:07 PM</t>
         </is>
       </c>
-      <c r="L25" s="5" t="inlineStr">
+      <c r="L27" s="5" t="inlineStr">
         <is>
           <t>9m</t>
         </is>
       </c>
-      <c r="M25" s="5" t="inlineStr">
+      <c r="M27" s="5" t="inlineStr">
         <is>
           <t>17h 19m</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1374642</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Shashi kumar thakur</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light in router  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light in router  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 08:22:33 AM</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 08:08:43 AM</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 01:43:44 PM</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>5h 21m</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>5h 35m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_19_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -3033,10 +3033,8 @@
           <t>Shashi kumar thakur</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>9818217448</t>
-        </is>
+      <c r="O14" s="3" t="n">
+        <v>9818217448</v>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
@@ -3126,10 +3124,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN14" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
@@ -3140,7 +3136,7 @@
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>Case : no light in router  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
@@ -3189,7 +3185,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -3859,7 +3855,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>Case : no light in router  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_19_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW14"/>
+  <dimension ref="A1:AW15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -3165,6 +3165,205 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 2:24 PM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>TKT1374360</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Rupan Shahi Thakuri</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>Rupan Shahi Thakuri</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>9843599958</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 02:24:08 PM</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>9843599958</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 03:51:58 PM</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 02:24:08 PM</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="inlineStr"/>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA15" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC15" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr">
+        <is>
+          <t>Dhapakhel, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF15" s="3" t="inlineStr"/>
+      <c r="AG15" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="3" t="inlineStr">
+        <is>
+          <t>04:24 hour</t>
+        </is>
+      </c>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>CDB473</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr"/>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>22h 32m</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3176,7 +3375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -3185,7 +3384,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -3213,7 +3412,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -3223,7 +3422,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -3234,7 +3433,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
@@ -3246,7 +3445,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>5h 45m</t>
+          <t>4h 47m</t>
         </is>
       </c>
     </row>
@@ -3258,7 +3457,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 17h 50m</t>
+          <t>1d 14h 37m</t>
         </is>
       </c>
     </row>
@@ -3299,14 +3498,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -3407,14 +3606,14 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -3889,6 +4088,73 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>TKT1374360</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Rupan Shahi Thakuri</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 02:24:08 PM</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 03:51:58 PM</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 02:24:08 PM</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>22h 32m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_19_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW15"/>
+  <dimension ref="A1:AW16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3232,10 +3232,8 @@
           <t>Rupan Shahi Thakuri</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>9843599958</t>
-        </is>
+      <c r="O15" s="3" t="n">
+        <v>9843599958</v>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
@@ -3321,10 +3319,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN15" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
@@ -3335,32 +3331,239 @@
       <c r="AQ15" s="3" t="inlineStr"/>
       <c r="AR15" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>22h 32m</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS15" s="3" t="inlineStr">
+      <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 2:46 PM</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue    has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>TKT1374322</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Badri Kuamar Rai</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Badri Kuamar Rai</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>9862297207</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 02:46:45 PM</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>9841168136</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 02:51:10 PM</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 02:46:45 PM</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr">
+        <is>
+          <t>27.648692</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr">
+        <is>
+          <t>Nakhipot Basket Ball court,Bishal Chowk - Nakhipot Rd, Lalitpur 44700, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF16" s="3" t="inlineStr">
+        <is>
+          <t>yalung3695@hotmail.com</t>
+        </is>
+      </c>
+      <c r="AG16" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr"/>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh Rawat</t>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>3,7</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr">
+        <is>
+          <t>85.317467</t>
+        </is>
+      </c>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue    has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT15" s="3" t="inlineStr">
-        <is>
-          <t>22h 32m</t>
-        </is>
-      </c>
-      <c r="AU15" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV15" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="AW15" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>23h 55m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue    has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
         </is>
       </c>
     </row>
@@ -3375,7 +3578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -3384,7 +3587,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -3412,7 +3615,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -3433,7 +3636,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -3516,14 +3719,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -3625,210 +3828,166 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Mesh Connectivity</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Extender Installation Request</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr"/>
-      <c r="B20" s="3" t="inlineStr"/>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Mesh Connectivity</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Extender Installation Request</t>
+        </is>
+      </c>
       <c r="C20" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr"/>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M23" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>TKT1374083</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Sitaram Karki</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>19 Oct 2026 10:50:02 AM</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>18 Oct 2026 09:10:27 AM</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>19 Oct 2026 10:50:02 AM</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>1d 1h 39m</t>
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>TKT1374481</t>
+          <t>TKT1374083</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Bidhya Syantang</t>
+          <t>Sitaram Karki</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -3858,22 +4017,22 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>Case : for wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>19 Oct 2026 11:52:09 AM</t>
+          <t>19 Oct 2026 10:50:02 AM</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>18 Oct 2026 06:34:55 PM</t>
+          <t>18 Oct 2026 09:10:27 AM</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>19 Oct 2026 11:52:09 AM</t>
+          <t>19 Oct 2026 10:50:02 AM</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
@@ -3883,19 +4042,19 @@
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>17h 17m</t>
+          <t>1d 1h 39m</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>TKT1368992</t>
+          <t>TKT1374481</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Nabina Shrestha</t>
+          <t>Bidhya Syantang</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -3910,12 +4069,12 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -3925,44 +4084,44 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Case : payment   has been updated by Sunil Chaudhary</t>
+          <t>Case : for wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>18 Oct 2026 12:37:29 PM</t>
+          <t>19 Oct 2026 11:52:09 AM</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>13 Oct 2026 12:35:14 PM</t>
+          <t>18 Oct 2026 06:34:55 PM</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>19 Oct 2026 11:54:21 AM</t>
+          <t>19 Oct 2026 11:52:09 AM</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>23h 16m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>5d 23h 19m</t>
+          <t>17h 17m</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TKT1374525</t>
+          <t>TKT1368992</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>MD Sakib</t>
+          <t>Nabina Shrestha</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -3992,54 +4151,54 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Rajesh Maharjan</t>
+          <t>Case : payment   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>19 Oct 2026 12:53:24 PM</t>
+          <t>18 Oct 2026 12:37:29 PM</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>18 Oct 2026 07:43:37 PM</t>
+          <t>13 Oct 2026 12:35:14 PM</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>19 Oct 2026 01:03:07 PM</t>
+          <t>19 Oct 2026 11:54:21 AM</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>9m</t>
+          <t>23h 16m</t>
         </is>
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>17h 19m</t>
+          <t>5d 23h 19m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TKT1374642</t>
+          <t>TKT1374525</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Shashi kumar thakur</t>
+          <t>MD Sakib</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -4059,97 +4218,164 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Case : no light in router  has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>19 Oct 2026 08:22:33 AM</t>
+          <t>19 Oct 2026 12:53:24 PM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>19 Oct 2026 08:08:43 AM</t>
+          <t>18 Oct 2026 07:43:37 PM</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>19 Oct 2026 01:43:44 PM</t>
+          <t>19 Oct 2026 01:03:07 PM</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>5h 21m</t>
+          <t>9m</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>5h 35m</t>
+          <t>17h 19m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
+          <t>TKT1374642</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Shashi kumar thakur</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Case : no light in router  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 08:22:33 AM</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 08:08:43 AM</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 01:43:44 PM</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>5h 21m</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>5h 35m</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
           <t>TKT1374360</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>Rupan Shahi Thakuri</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F30" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
         <is>
           <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="I30" s="3" t="inlineStr">
         <is>
           <t>19 Oct 2026 02:24:08 PM</t>
         </is>
       </c>
-      <c r="J29" s="5" t="inlineStr">
+      <c r="J30" s="3" t="inlineStr">
         <is>
           <t>18 Oct 2026 03:51:58 PM</t>
         </is>
       </c>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="K30" s="3" t="inlineStr">
         <is>
           <t>19 Oct 2026 02:24:08 PM</t>
         </is>
       </c>
-      <c r="L29" s="5" t="inlineStr">
+      <c r="L30" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M29" s="5" t="inlineStr">
+      <c r="M30" s="3" t="inlineStr">
         <is>
           <t>22h 32m</t>
         </is>

--- a/audit_report_ALL_TEAM_19_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW16"/>
+  <dimension ref="A1:AW20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -496,10 +496,10 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="23" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -3427,10 +3427,8 @@
           <t>Badri Kuamar Rai</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>9862297207</t>
-        </is>
+      <c r="O16" s="3" t="n">
+        <v>9862297207</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
@@ -3465,10 +3463,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y16" s="3" t="inlineStr">
-        <is>
-          <t>27.648692</t>
-        </is>
+      <c r="Y16" s="3" t="n">
+        <v>27.648692</v>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
@@ -3520,50 +3516,882 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN16" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
           <t>3,7</t>
         </is>
       </c>
-      <c r="AP16" s="3" t="inlineStr">
-        <is>
-          <t>85.317467</t>
-        </is>
+      <c r="AP16" s="3" t="n">
+        <v>85.31746699999999</v>
       </c>
       <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>23h 55m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
           <t>Case : iptv issue    has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS16" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT16" s="3" t="inlineStr">
-        <is>
-          <t>23h 55m</t>
-        </is>
-      </c>
-      <c r="AU16" s="3" t="inlineStr">
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 2:54 PM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>router upgrade</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>TKT1373682</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Mukunda Bahadur Thapa</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Mukunda Bahadur Thapa</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>9851062963</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 02:33:43 PM</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>9851062963</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 02:33:43 PM</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 02:54:57 PM</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr">
+        <is>
+          <t>27.747679</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>Near Jeevan Jyoti English Boarding School., Manamaiju Bridge, 44600, Loktantrik Chowk, Manamaiju Bri</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="inlineStr"/>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr"/>
+      <c r="AI17" s="3" t="inlineStr"/>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>3,1</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr">
+        <is>
+          <t>85.304983</t>
+        </is>
+      </c>
+      <c r="AQ17" s="3" t="inlineStr"/>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>2d 21m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>2d 21m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
         <is>
           <t>Other / In Progress (On Hold)</t>
         </is>
       </c>
-      <c r="AV16" s="3" t="inlineStr">
-        <is>
-          <t>Case : iptv issue    has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="AW16" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Issue</t>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 2:55 PM</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi-6 instal   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>Wifi-6 instal</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>TKT1374258</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Om Prakash Shah</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Om Prakash Shah</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>9803089784</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:48:23 PM</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>9803725938O</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:48:23 PM</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 02:55:47 PM</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr">
+        <is>
+          <t>27.69812</t>
+        </is>
+      </c>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA18" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC18" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu,Kalanki,Himshikhar School, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF18" s="3" t="inlineStr">
+        <is>
+          <t>kumarrajiv1357@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG18" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH18" s="3" t="inlineStr"/>
+      <c r="AI18" s="3" t="inlineStr">
+        <is>
+          <t>04:55 hour</t>
+        </is>
+      </c>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr">
+        <is>
+          <t>Rajnikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>2,9</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr">
+        <is>
+          <t>85.27145</t>
+        </is>
+      </c>
+      <c r="AQ18" s="3" t="inlineStr"/>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi-6 instal   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 7m</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 7m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi-6 instal   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 2:54 PM</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>Wifi-6 instal</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>TKT1374258</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Om Prakash Shah</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>Om Prakash Shah</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>9803089784</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:48:23 PM</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>9803725938O</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:48:23 PM</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 02:55:47 PM</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr">
+        <is>
+          <t>27.69812</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA19" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC19" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu,Kalanki,Himshikhar School, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF19" s="3" t="inlineStr">
+        <is>
+          <t>kumarrajiv1357@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG19" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr">
+        <is>
+          <t>04:55 hour</t>
+        </is>
+      </c>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr">
+        <is>
+          <t>Rajnikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>2,9</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr">
+        <is>
+          <t>85.27145</t>
+        </is>
+      </c>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 7m</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 7m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 2:53 PM</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>TKT1373602</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Spandan Bhatta</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Spandan Bhatta</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>9841400178</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 12:38:52 PM</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>9869382682</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 12:38:52 PM</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 02:54:16 PM</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="inlineStr">
+        <is>
+          <t>27.7376</t>
+        </is>
+      </c>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA20" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC20" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD20" s="3" t="inlineStr"/>
+      <c r="AE20" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF20" s="3" t="inlineStr">
+        <is>
+          <t>bhattalaxman2@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG20" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH20" s="3" t="inlineStr"/>
+      <c r="AI20" s="3" t="inlineStr">
+        <is>
+          <t>12:15 hour</t>
+        </is>
+      </c>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM20" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN20" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>4,15</t>
+        </is>
+      </c>
+      <c r="AP20" s="3" t="inlineStr">
+        <is>
+          <t>85.28823</t>
+        </is>
+      </c>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 15m</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 15m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -3578,7 +4406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -3587,7 +4415,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -3615,7 +4443,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -3625,7 +4453,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -3636,7 +4464,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>47.4%</t>
         </is>
       </c>
     </row>
@@ -3648,7 +4476,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>4h 47m</t>
+          <t>14h 35m</t>
         </is>
       </c>
     </row>
@@ -3660,7 +4488,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 14h 37m</t>
+          <t>1d 13h 8m</t>
         </is>
       </c>
     </row>
@@ -3701,14 +4529,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -3809,14 +4637,14 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -4381,6 +5209,207 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>TKT1374258</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Om Prakash Shah</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi-6 instal   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi-6 instal   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:48:23 PM</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:48:23 PM</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 02:55:47 PM</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>1d 2h 7m</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>1d 2h 7m</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1374258</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Om Prakash Shah</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:48:23 PM</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:48:23 PM</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 02:55:47 PM</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 7m</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 7m</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>TKT1373602</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Spandan Bhatta</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 12:38:52 PM</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 12:38:52 PM</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 02:54:16 PM</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>2d 2h 15m</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>2d 2h 15m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_19_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -3626,10 +3626,8 @@
           <t>Mukunda Bahadur Thapa</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>9851062963</t>
-        </is>
+      <c r="O17" s="3" t="n">
+        <v>9851062963</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
@@ -3664,10 +3662,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y17" s="3" t="inlineStr">
-        <is>
-          <t>27.747679</t>
-        </is>
+      <c r="Y17" s="3" t="n">
+        <v>27.747679</v>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
@@ -3715,25 +3711,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN17" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
           <t>3,1</t>
         </is>
       </c>
-      <c r="AP17" s="3" t="inlineStr">
-        <is>
-          <t>85.304983</t>
-        </is>
+      <c r="AP17" s="3" t="n">
+        <v>85.30498299999999</v>
       </c>
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
@@ -3829,10 +3821,8 @@
           <t>Om Prakash Shah</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>9803089784</t>
-        </is>
+      <c r="O18" s="3" t="n">
+        <v>9803089784</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
@@ -3867,10 +3857,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y18" s="3" t="inlineStr">
-        <is>
-          <t>27.69812</t>
-        </is>
+      <c r="Y18" s="3" t="n">
+        <v>27.69812</v>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
@@ -3926,25 +3914,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN18" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
           <t>2,9</t>
         </is>
       </c>
-      <c r="AP18" s="3" t="inlineStr">
-        <is>
-          <t>85.27145</t>
-        </is>
+      <c r="AP18" s="3" t="n">
+        <v>85.27145</v>
       </c>
       <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi-6 instal   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
@@ -4040,10 +4024,8 @@
           <t>Om Prakash Shah</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>9803089784</t>
-        </is>
+      <c r="O19" s="3" t="n">
+        <v>9803089784</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
@@ -4078,10 +4060,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y19" s="3" t="inlineStr">
-        <is>
-          <t>27.69812</t>
-        </is>
+      <c r="Y19" s="3" t="n">
+        <v>27.69812</v>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
@@ -4137,25 +4117,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN19" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
           <t>2,9</t>
         </is>
       </c>
-      <c r="AP19" s="3" t="inlineStr">
-        <is>
-          <t>85.27145</t>
-        </is>
+      <c r="AP19" s="3" t="n">
+        <v>85.27145</v>
       </c>
       <c r="AQ19" s="3" t="inlineStr"/>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
@@ -4251,10 +4227,8 @@
           <t>Spandan Bhatta</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>9841400178</t>
-        </is>
+      <c r="O20" s="3" t="n">
+        <v>9841400178</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
@@ -4289,10 +4263,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y20" s="3" t="inlineStr">
-        <is>
-          <t>27.7376</t>
-        </is>
+      <c r="Y20" s="3" t="n">
+        <v>27.7376</v>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
@@ -4348,25 +4320,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN20" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN20" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
           <t>4,15</t>
         </is>
       </c>
-      <c r="AP20" s="3" t="inlineStr">
-        <is>
-          <t>85.28823</t>
-        </is>
+      <c r="AP20" s="3" t="n">
+        <v>85.28823</v>
       </c>
       <c r="AQ20" s="3" t="inlineStr"/>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
@@ -4415,7 +4383,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -5242,7 +5210,7 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi-6 instal   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
@@ -5309,7 +5277,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
@@ -5376,7 +5344,7 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_19_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW20"/>
+  <dimension ref="A1:AW22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -4363,6 +4363,412 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 3:27 PM</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Case : HARDWARE DAMAGE ISSUE   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>HARDWARE DAMAGE ISSUE</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>TKT1374881</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Shashi kumar thakur</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Shashi kumar thakur</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>9818217448</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 02:12:59 PM</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>KLK9818217448</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 02:10:22 PM</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 03:27:12 PM</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr"/>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr"/>
+      <c r="AE21" s="3" t="inlineStr">
+        <is>
+          <t>Goldhunga Orchid Academy Goldhunga Orchid Academy - School P7WW+JJ5 Kathmandu 44600, Kathmandu, Nepa</t>
+        </is>
+      </c>
+      <c r="AF21" s="3" t="inlineStr">
+        <is>
+          <t>9818217448@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG21" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH21" s="3" t="inlineStr"/>
+      <c r="AI21" s="3" t="inlineStr">
+        <is>
+          <t>01:16 hour</t>
+        </is>
+      </c>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr">
+        <is>
+          <t>Sanam Sadar</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>L58-2</t>
+        </is>
+      </c>
+      <c r="AP21" s="3" t="inlineStr"/>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>Case : HARDWARE DAMAGE ISSUE   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>1h 14m</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>1h 16m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>Case : HARDWARE DAMAGE ISSUE   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 3:26 PM</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : HARDWARE DAMAGE ISSUE   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>HARDWARE DAMAGE ISSUE</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1374881</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Shashi kumar thakur</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Shashi kumar thakur</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>9818217448</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 02:12:59 PM</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="inlineStr"/>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>KLK9818217448</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 02:10:22 PM</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 03:27:12 PM</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y22" s="3" t="inlineStr"/>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA22" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC22" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD22" s="3" t="inlineStr"/>
+      <c r="AE22" s="3" t="inlineStr">
+        <is>
+          <t>Goldhunga Orchid Academy Goldhunga Orchid Academy - School P7WW+JJ5 Kathmandu 44600, Kathmandu, Nepa</t>
+        </is>
+      </c>
+      <c r="AF22" s="3" t="inlineStr">
+        <is>
+          <t>9818217448@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG22" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH22" s="3" t="inlineStr"/>
+      <c r="AI22" s="3" t="inlineStr">
+        <is>
+          <t>01:16 hour</t>
+        </is>
+      </c>
+      <c r="AJ22" s="3" t="inlineStr"/>
+      <c r="AK22" s="3" t="inlineStr"/>
+      <c r="AL22" s="3" t="inlineStr">
+        <is>
+          <t>Sanam Sadar</t>
+        </is>
+      </c>
+      <c r="AM22" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN22" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>L58-2</t>
+        </is>
+      </c>
+      <c r="AP22" s="3" t="inlineStr"/>
+      <c r="AQ22" s="3" t="inlineStr"/>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>Case : HARDWARE DAMAGE ISSUE   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>1h 14m</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>1h 16m</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
+          <t>Case : HARDWARE DAMAGE ISSUE   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4374,16 +4780,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -4411,7 +4817,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -4421,7 +4827,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -4432,7 +4838,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>52.4%</t>
         </is>
       </c>
     </row>
@@ -4444,7 +4850,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>14h 35m</t>
+          <t>12h 9m</t>
         </is>
       </c>
     </row>
@@ -4456,7 +4862,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 13h 8m</t>
+          <t>1d 6h 36m</t>
         </is>
       </c>
     </row>
@@ -4515,14 +4921,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -4647,14 +5053,14 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
@@ -4665,192 +5071,148 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Mesh Connectivity</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Extender Installation Request</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr"/>
-      <c r="B21" s="5" t="inlineStr"/>
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Mesh Connectivity</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Extender Installation Request</t>
+        </is>
+      </c>
       <c r="C21" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr"/>
+      <c r="B22" s="3" t="inlineStr"/>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L24" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M24" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>TKT1374083</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Sitaram Karki</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>19 Oct 2026 10:50:02 AM</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>18 Oct 2026 09:10:27 AM</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>19 Oct 2026 10:50:02 AM</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>1d 1h 39m</t>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>TKT1374481</t>
+          <t>TKT1374083</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Bidhya Syantang</t>
+          <t>Sitaram Karki</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -4880,22 +5242,22 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Case : for wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>19 Oct 2026 11:52:09 AM</t>
+          <t>19 Oct 2026 10:50:02 AM</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>18 Oct 2026 06:34:55 PM</t>
+          <t>18 Oct 2026 09:10:27 AM</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>19 Oct 2026 11:52:09 AM</t>
+          <t>19 Oct 2026 10:50:02 AM</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
@@ -4905,19 +5267,19 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>17h 17m</t>
+          <t>1d 1h 39m</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TKT1368992</t>
+          <t>TKT1374481</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Nabina Shrestha</t>
+          <t>Bidhya Syantang</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -4932,12 +5294,12 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -4947,44 +5309,44 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Case : payment   has been updated by Sunil Chaudhary</t>
+          <t>Case : for wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>18 Oct 2026 12:37:29 PM</t>
+          <t>19 Oct 2026 11:52:09 AM</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>13 Oct 2026 12:35:14 PM</t>
+          <t>18 Oct 2026 06:34:55 PM</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>19 Oct 2026 11:54:21 AM</t>
+          <t>19 Oct 2026 11:52:09 AM</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>23h 16m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>5d 23h 19m</t>
+          <t>17h 17m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TKT1374525</t>
+          <t>TKT1368992</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>MD Sakib</t>
+          <t>Nabina Shrestha</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -5014,54 +5376,54 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Rajesh Maharjan</t>
+          <t>Case : payment   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>19 Oct 2026 12:53:24 PM</t>
+          <t>18 Oct 2026 12:37:29 PM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>18 Oct 2026 07:43:37 PM</t>
+          <t>13 Oct 2026 12:35:14 PM</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>19 Oct 2026 01:03:07 PM</t>
+          <t>19 Oct 2026 11:54:21 AM</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>9m</t>
+          <t>23h 16m</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>17h 19m</t>
+          <t>5d 23h 19m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1374642</t>
+          <t>TKT1374525</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Shashi kumar thakur</t>
+          <t>MD Sakib</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -5081,64 +5443,64 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : no light in router  has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>19 Oct 2026 08:22:33 AM</t>
+          <t>19 Oct 2026 12:53:24 PM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>19 Oct 2026 08:08:43 AM</t>
+          <t>18 Oct 2026 07:43:37 PM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>19 Oct 2026 01:43:44 PM</t>
+          <t>19 Oct 2026 01:03:07 PM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>5h 21m</t>
+          <t>9m</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>5h 35m</t>
+          <t>17h 19m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1374360</t>
+          <t>TKT1374642</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Rupan Shahi Thakuri</t>
+          <t>Shashi kumar thakur</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -5148,44 +5510,44 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>Case : no light in router  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>19 Oct 2026 02:24:08 PM</t>
+          <t>19 Oct 2026 08:22:33 AM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>18 Oct 2026 03:51:58 PM</t>
+          <t>19 Oct 2026 08:08:43 AM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>19 Oct 2026 02:24:08 PM</t>
+          <t>19 Oct 2026 01:43:44 PM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>5h 21m</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>22h 32m</t>
+          <t>5h 35m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1374258</t>
+          <t>TKT1374360</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Om Prakash Shah</t>
+          <t>Rupan Shahi Thakuri</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -5200,12 +5562,12 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -5215,32 +5577,32 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi-6 instal   has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>18 Oct 2026 12:48:23 PM</t>
+          <t>19 Oct 2026 02:24:08 PM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>18 Oct 2026 12:48:23 PM</t>
+          <t>18 Oct 2026 03:51:58 PM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>19 Oct 2026 02:55:47 PM</t>
+          <t>19 Oct 2026 02:24:08 PM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>1d 2h 7m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>1d 2h 7m</t>
+          <t>22h 32m</t>
         </is>
       </c>
     </row>
@@ -5282,7 +5644,7 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : Wifi-6 instal   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -5314,67 +5676,268 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
+          <t>TKT1374258</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Om Prakash Shah</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:48:23 PM</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 12:48:23 PM</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 02:55:47 PM</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>1d 2h 7m</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>1d 2h 7m</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
           <t>TKT1373602</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>Spandan Bhatta</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="G34" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H33" s="5" t="inlineStr">
+      <c r="H34" s="3" t="inlineStr">
         <is>
           <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="I34" s="3" t="inlineStr">
         <is>
           <t>17 Oct 2026 12:38:52 PM</t>
         </is>
       </c>
-      <c r="J33" s="5" t="inlineStr">
+      <c r="J34" s="3" t="inlineStr">
         <is>
           <t>17 Oct 2026 12:38:52 PM</t>
         </is>
       </c>
-      <c r="K33" s="5" t="inlineStr">
+      <c r="K34" s="3" t="inlineStr">
         <is>
           <t>19 Oct 2026 02:54:16 PM</t>
         </is>
       </c>
-      <c r="L33" s="5" t="inlineStr">
+      <c r="L34" s="3" t="inlineStr">
         <is>
           <t>2d 2h 15m</t>
         </is>
       </c>
-      <c r="M33" s="5" t="inlineStr">
+      <c r="M34" s="3" t="inlineStr">
         <is>
           <t>2d 2h 15m</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>TKT1374881</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Shashi kumar thakur</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Case : HARDWARE DAMAGE ISSUE   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>Case : HARDWARE DAMAGE ISSUE   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 02:12:59 PM</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 02:10:22 PM</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 03:27:12 PM</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>1h 14m</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>1h 16m</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1374881</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Shashi kumar thakur</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>Case : HARDWARE DAMAGE ISSUE   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : HARDWARE DAMAGE ISSUE   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 02:12:59 PM</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 02:10:22 PM</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 03:27:12 PM</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>1h 14m</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>1h 16m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_19_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW22"/>
+  <dimension ref="A1:AW25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4430,10 +4430,8 @@
           <t>Shashi kumar thakur</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>9818217448</t>
-        </is>
+      <c r="O21" s="3" t="n">
+        <v>9818217448</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
@@ -4523,10 +4521,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN21" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
@@ -4537,7 +4533,7 @@
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>Case : HARDWARE DAMAGE ISSUE   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
@@ -4633,10 +4629,8 @@
           <t>Shashi kumar thakur</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>9818217448</t>
-        </is>
+      <c r="O22" s="3" t="n">
+        <v>9818217448</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
@@ -4726,10 +4720,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN22" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
@@ -4740,32 +4732,645 @@
       <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>1h 14m</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>1h 16m</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
           <t>Case : HARDWARE DAMAGE ISSUE   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS22" s="3" t="inlineStr">
-        <is>
-          <t>1h 14m</t>
-        </is>
-      </c>
-      <c r="AT22" s="3" t="inlineStr">
-        <is>
-          <t>1h 16m</t>
-        </is>
-      </c>
-      <c r="AU22" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV22" s="3" t="inlineStr">
-        <is>
-          <t>Case : HARDWARE DAMAGE ISSUE   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW22" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 3:46 PM</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>TKT1374369</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>Leela Bahad Neupane</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>Leela Bahad Neupane</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>9841316684</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 04:01:15 PM</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr"/>
+      <c r="T23" s="3" t="inlineStr"/>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>9841316684</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 04:01:15 PM</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 03:46:49 PM</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y23" s="3" t="inlineStr"/>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA23" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB23" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC23" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD23" s="3" t="inlineStr"/>
+      <c r="AE23" s="3" t="inlineStr">
+        <is>
+          <t>near by Balaju bypass - Clothing store, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF23" s="3" t="inlineStr">
+        <is>
+          <t>9841316684@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG23" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH23" s="3" t="inlineStr"/>
+      <c r="AI23" s="3" t="inlineStr"/>
+      <c r="AJ23" s="3" t="inlineStr"/>
+      <c r="AK23" s="3" t="inlineStr"/>
+      <c r="AL23" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM23" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN23" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO23" s="3" t="inlineStr">
+        <is>
+          <t>CDB081</t>
+        </is>
+      </c>
+      <c r="AP23" s="3" t="inlineStr"/>
+      <c r="AQ23" s="3" t="inlineStr"/>
+      <c r="AR23" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>23h 45m</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>23h 45m</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW23" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 3:46 PM</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1374291</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>Sarad Tamang</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>Sarad Tamang</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>9851085081</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 03:46:35 PM</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>CHB9851085081</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 01:47:48 PM</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 03:46:35 PM</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA24" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB24" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC24" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD24" s="3" t="inlineStr"/>
+      <c r="AE24" s="3" t="inlineStr">
+        <is>
+          <t>Jeevan Tara Academy - Higher secondary school Kathmandu 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF24" s="3" t="inlineStr">
+        <is>
+          <t>9851085081@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG24" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH24" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI24" s="3" t="inlineStr">
+        <is>
+          <t>05:46 hour</t>
+        </is>
+      </c>
+      <c r="AJ24" s="3" t="inlineStr"/>
+      <c r="AK24" s="3" t="inlineStr"/>
+      <c r="AL24" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM24" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN24" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO24" s="3" t="inlineStr">
+        <is>
+          <t>L37-6</t>
+        </is>
+      </c>
+      <c r="AP24" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ24" s="3" t="inlineStr"/>
+      <c r="AR24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 58m</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW24" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 3:45 PM</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>TKT1373226</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Prabin Mainali</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>Prabin Mainali</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>9851330557</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 03:45:30 PM</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="3" t="inlineStr"/>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>9851330557</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 08:13:58 PM</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 03:45:30 PM</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr"/>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA25" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB25" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC25" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD25" s="3" t="inlineStr"/>
+      <c r="AE25" s="3" t="inlineStr">
+        <is>
+          <t>27.75457483862807, 85.32602632379277, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF25" s="3" t="inlineStr"/>
+      <c r="AG25" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH25" s="3" t="inlineStr"/>
+      <c r="AI25" s="3" t="inlineStr">
+        <is>
+          <t>15:45 hour</t>
+        </is>
+      </c>
+      <c r="AJ25" s="3" t="inlineStr"/>
+      <c r="AK25" s="3" t="inlineStr"/>
+      <c r="AL25" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO25" s="3" t="inlineStr">
+        <is>
+          <t>L36-1</t>
+        </is>
+      </c>
+      <c r="AP25" s="3" t="inlineStr"/>
+      <c r="AQ25" s="3" t="inlineStr"/>
+      <c r="AR25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>2d 19h 31m</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW25" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -4780,7 +5385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -4817,7 +5422,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -4827,7 +5432,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -4838,7 +5443,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>54.2%</t>
         </is>
       </c>
     </row>
@@ -4850,7 +5455,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>12h 9m</t>
+          <t>10h 17m</t>
         </is>
       </c>
     </row>
@@ -4862,7 +5467,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 6h 36m</t>
+          <t>1d 9h 5m</t>
         </is>
       </c>
     </row>
@@ -4903,14 +5508,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>58.8%</t>
         </is>
       </c>
     </row>
@@ -5011,14 +5616,14 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>58.8%</t>
         </is>
       </c>
     </row>
@@ -5840,7 +6445,7 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Case : HARDWARE DAMAGE ISSUE   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
@@ -5907,14 +6512,14 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
           <t>Case : HARDWARE DAMAGE ISSUE   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>Case : HARDWARE DAMAGE ISSUE   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
           <t>19 Oct 2026 02:12:59 PM</t>
@@ -5938,6 +6543,140 @@
       <c r="M36" s="3" t="inlineStr">
         <is>
           <t>1h 16m</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>TKT1374291</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Sarad Tamang</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 03:46:35 PM</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 01:47:48 PM</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 03:46:35 PM</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>1d 1h 58m</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1373226</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Prabin Mainali</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 03:45:30 PM</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 08:13:58 PM</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 03:45:30 PM</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>2d 19h 31m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_19_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW25"/>
+  <dimension ref="A1:AW26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -4828,10 +4828,8 @@
           <t>Leela Bahad Neupane</t>
         </is>
       </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>9841316684</t>
-        </is>
+      <c r="O23" s="3" t="n">
+        <v>9841316684</v>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
@@ -4917,10 +4915,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN23" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN23" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
@@ -4931,7 +4927,7 @@
       <c r="AQ23" s="3" t="inlineStr"/>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
@@ -5027,10 +5023,8 @@
           <t>Sarad Tamang</t>
         </is>
       </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>9851085081</t>
-        </is>
+      <c r="O24" s="3" t="n">
+        <v>9851085081</v>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
@@ -5065,10 +5059,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y24" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y24" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
@@ -5106,10 +5098,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH24" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH24" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI24" s="3" t="inlineStr">
         <is>
@@ -5128,25 +5118,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN24" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN24" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
           <t>L37-6</t>
         </is>
       </c>
-      <c r="AP24" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP24" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ24" s="3" t="inlineStr"/>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
@@ -5232,20 +5218,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M25" s="3" t="inlineStr"/>
       <c r="N25" s="3" t="inlineStr">
         <is>
           <t>Prabin Mainali</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>9851330557</t>
-        </is>
+      <c r="O25" s="3" t="n">
+        <v>9851330557</v>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
@@ -5331,10 +5311,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN25" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN25" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
@@ -5345,30 +5323,133 @@
       <c r="AQ25" s="3" t="inlineStr"/>
       <c r="AR25" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>2d 19h 31m</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS25" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT25" s="3" t="inlineStr">
-        <is>
-          <t>2d 19h 31m</t>
-        </is>
-      </c>
-      <c r="AU25" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV25" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="AW25" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Om Neupane</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 3:54 PM</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>A46UWsNL7J/c+OCnFBgFhw==</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Om Neupane</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Om Neupane</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr"/>
+      <c r="J26" s="3" t="inlineStr"/>
+      <c r="K26" s="3" t="inlineStr"/>
+      <c r="L26" s="3" t="inlineStr"/>
+      <c r="M26" s="3" t="inlineStr"/>
+      <c r="N26" s="3" t="inlineStr"/>
+      <c r="O26" s="3" t="inlineStr"/>
+      <c r="P26" s="3" t="inlineStr"/>
+      <c r="Q26" s="3" t="inlineStr"/>
+      <c r="R26" s="3" t="inlineStr"/>
+      <c r="S26" s="3" t="inlineStr"/>
+      <c r="T26" s="3" t="inlineStr"/>
+      <c r="U26" s="3" t="inlineStr"/>
+      <c r="V26" s="3" t="inlineStr"/>
+      <c r="W26" s="3" t="inlineStr"/>
+      <c r="X26" s="3" t="inlineStr"/>
+      <c r="Y26" s="3" t="inlineStr"/>
+      <c r="Z26" s="3" t="inlineStr"/>
+      <c r="AA26" s="3" t="inlineStr"/>
+      <c r="AB26" s="3" t="inlineStr"/>
+      <c r="AC26" s="3" t="inlineStr"/>
+      <c r="AD26" s="3" t="inlineStr"/>
+      <c r="AE26" s="3" t="inlineStr"/>
+      <c r="AF26" s="3" t="inlineStr"/>
+      <c r="AG26" s="3" t="inlineStr"/>
+      <c r="AH26" s="3" t="inlineStr"/>
+      <c r="AI26" s="3" t="inlineStr"/>
+      <c r="AJ26" s="3" t="inlineStr"/>
+      <c r="AK26" s="3" t="inlineStr"/>
+      <c r="AL26" s="3" t="inlineStr"/>
+      <c r="AM26" s="3" t="inlineStr"/>
+      <c r="AN26" s="3" t="inlineStr"/>
+      <c r="AO26" s="3" t="inlineStr"/>
+      <c r="AP26" s="3" t="inlineStr"/>
+      <c r="AQ26" s="3" t="inlineStr"/>
+      <c r="AR26" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV26" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Om Neupane</t>
+        </is>
+      </c>
+      <c r="AW26" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -5394,7 +5475,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -5422,7 +5503,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -5443,7 +5524,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>52.0%</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6660,7 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
@@ -6646,7 +6727,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_19_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW26"/>
+  <dimension ref="A1:AW27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -517,7 +517,7 @@
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="11" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="29" customWidth="1" min="32" max="32"/>
+    <col width="31" customWidth="1" min="32" max="32"/>
     <col width="32" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -5455,6 +5455,217 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 4:27 PM</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi-6 router instal   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>Wifi-6 router instal</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>TKT1374092</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>Sabnam Bhandari</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>Sabnam Bhandari</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>9801106961</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 09:26:21 AM</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr"/>
+      <c r="T27" s="3" t="inlineStr"/>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t>IC9801106961</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 09:26:21 AM</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 04:27:47 PM</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y27" s="3" t="inlineStr">
+        <is>
+          <t>27.69034</t>
+        </is>
+      </c>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA27" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB27" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC27" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD27" s="3" t="inlineStr"/>
+      <c r="AE27" s="3" t="inlineStr">
+        <is>
+          <t>Near Adarsa Fustal, M7QC+VC7, Chandragiri, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF27" s="3" t="inlineStr">
+        <is>
+          <t>sabnambhandari2015@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG27" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH27" s="3" t="inlineStr"/>
+      <c r="AI27" s="3" t="inlineStr">
+        <is>
+          <t>06:27 hour</t>
+        </is>
+      </c>
+      <c r="AJ27" s="3" t="inlineStr"/>
+      <c r="AK27" s="3" t="inlineStr"/>
+      <c r="AL27" s="3" t="inlineStr">
+        <is>
+          <t>Rajnikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM27" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN27" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO27" s="3" t="inlineStr">
+        <is>
+          <t>2,5</t>
+        </is>
+      </c>
+      <c r="AP27" s="3" t="inlineStr">
+        <is>
+          <t>85.26937</t>
+        </is>
+      </c>
+      <c r="AQ27" s="3" t="inlineStr"/>
+      <c r="AR27" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi-6 router instal   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS27" s="3" t="inlineStr">
+        <is>
+          <t>1d 7h 1m</t>
+        </is>
+      </c>
+      <c r="AT27" s="3" t="inlineStr">
+        <is>
+          <t>1d 7h 1m</t>
+        </is>
+      </c>
+      <c r="AU27" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV27" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi-6 router instal   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW27" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5466,7 +5677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -5475,7 +5686,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -5503,7 +5714,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
@@ -5513,7 +5724,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -5524,7 +5735,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>53.8%</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5747,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>10h 17m</t>
+          <t>11h 46m</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5759,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 9h 5m</t>
+          <t>1d 8h 57m</t>
         </is>
       </c>
     </row>
@@ -5589,14 +5800,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>61.1%</t>
         </is>
       </c>
     </row>
@@ -5697,14 +5908,14 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>61.1%</t>
         </is>
       </c>
     </row>
@@ -6761,6 +6972,73 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>TKT1374092</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Sabnam Bhandari</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi-6 router instal   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi-6 router instal   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 09:26:21 AM</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 09:26:21 AM</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 04:27:47 PM</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>1d 7h 1m</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>1d 7h 1m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_19_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_19_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -5522,10 +5522,8 @@
           <t>Sabnam Bhandari</t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t>9801106961</t>
-        </is>
+      <c r="O27" s="3" t="n">
+        <v>9801106961</v>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
@@ -5560,10 +5558,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y27" s="3" t="inlineStr">
-        <is>
-          <t>27.69034</t>
-        </is>
+      <c r="Y27" s="3" t="n">
+        <v>27.69034</v>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
@@ -5619,25 +5615,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN27" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN27" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
           <t>2,5</t>
         </is>
       </c>
-      <c r="AP27" s="3" t="inlineStr">
-        <is>
-          <t>85.26937</t>
-        </is>
+      <c r="AP27" s="3" t="n">
+        <v>85.26937</v>
       </c>
       <c r="AQ27" s="3" t="inlineStr"/>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi-6 router instal   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
@@ -5686,7 +5678,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -7005,7 +6997,7 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi-6 router instal   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
